--- a/URL 설계서.xlsx
+++ b/URL 설계서.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\미니프로젝트\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\git\java-ymca-mini-project\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E676FE12-9DFC-4BEF-A47A-39679AF8FAAD}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9ADE9024-8147-4C7D-B4FB-05E2C5DA0242}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -274,46 +274,16 @@
     <t>주문</t>
   </si>
   <si>
-    <t>GET /order/list</t>
-  </si>
-  <si>
-    <t>OrderController</t>
-  </si>
-  <si>
-    <t>getOrderList()</t>
-  </si>
-  <si>
-    <t>Order</t>
-  </si>
-  <si>
     <t>주문 목록</t>
-  </si>
-  <si>
-    <t>getOrderDetail()</t>
   </si>
   <si>
     <t>주문 상세정보</t>
   </si>
   <si>
-    <t>POST /order/create</t>
-  </si>
-  <si>
-    <t>createOrder()</t>
-  </si>
-  <si>
     <t>주문 생성</t>
   </si>
   <si>
-    <t>cancelOrder()</t>
-  </si>
-  <si>
     <t>주문 취소</t>
-  </si>
-  <si>
-    <t>GET /order/history</t>
-  </si>
-  <si>
-    <t>getOrderHistory()</t>
   </si>
   <si>
     <t>주문 이력 조회</t>
@@ -409,12 +379,6 @@
     <t>GET /board/detail/{board_idx}</t>
   </si>
   <si>
-    <t>POST /order/cancel/{order_idx}</t>
-  </si>
-  <si>
-    <t>GET /order/detail/{order_idx}</t>
-  </si>
-  <si>
     <t>POST /cart/remove/{cart_item_idx}</t>
   </si>
   <si>
@@ -463,15 +427,6 @@
     <t>views/item/item_search.jsp</t>
   </si>
   <si>
-    <t>views/order/order_list.jsp</t>
-  </si>
-  <si>
-    <t>views/order/order_detail.jsp</t>
-  </si>
-  <si>
-    <t>views/order/order_checkout.jsp</t>
-  </si>
-  <si>
     <t>views/board/board_list.jsp</t>
   </si>
   <si>
@@ -482,6 +437,51 @@
   </si>
   <si>
     <t>views/board/board_edit.jsp</t>
+  </si>
+  <si>
+    <t>views/orders/orders_list.jsp</t>
+  </si>
+  <si>
+    <t>views/orders/orders_detail.jsp</t>
+  </si>
+  <si>
+    <t>views/orders/orders_checkout.jsp</t>
+  </si>
+  <si>
+    <t>GET /orders/list</t>
+  </si>
+  <si>
+    <t>GET /orders/detail/{orders_idx}</t>
+  </si>
+  <si>
+    <t>POST /orders/create</t>
+  </si>
+  <si>
+    <t>POST /orders/cancel/{orders_idx}</t>
+  </si>
+  <si>
+    <t>GET /orders/history</t>
+  </si>
+  <si>
+    <t>Orders</t>
+  </si>
+  <si>
+    <t>OrdersController</t>
+  </si>
+  <si>
+    <t>getOrdersList()</t>
+  </si>
+  <si>
+    <t>getOrdersDetail()</t>
+  </si>
+  <si>
+    <t>createOrders()</t>
+  </si>
+  <si>
+    <t>cancelOrders()</t>
+  </si>
+  <si>
+    <t>getOrdersHistory()</t>
   </si>
 </sst>
 </file>
@@ -897,9 +897,7 @@
         <left style="thin">
           <color indexed="64"/>
         </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
+        <right/>
         <top/>
         <bottom/>
       </border>
@@ -923,7 +921,9 @@
         <left style="thin">
           <color indexed="64"/>
         </left>
-        <right/>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
         <top/>
         <bottom/>
       </border>
@@ -1105,12 +1105,12 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="프로젝트_기능표" displayName="프로젝트_기능표" ref="C3:I37" headerRowDxfId="10" dataDxfId="9" totalsRowDxfId="7" tableBorderDxfId="8">
   <tableColumns count="7">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="기능" dataDxfId="6"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="API/URL" dataDxfId="0"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Controller" dataDxfId="5"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Method" dataDxfId="4"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="JSP 경로" dataDxfId="1"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="VO/Entity" dataDxfId="3"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="설명" dataDxfId="2"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="API/URL" dataDxfId="5"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Controller" dataDxfId="4"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Method" dataDxfId="3"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="JSP 경로" dataDxfId="2"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="VO/Entity" dataDxfId="1"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="설명" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="시트1-style" showFirstColumn="1" showLastColumn="1" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1610,7 +1610,7 @@
         <v>7</v>
       </c>
       <c r="D8" s="54" t="s">
-        <v>138</v>
+        <v>126</v>
       </c>
       <c r="E8" s="5" t="s">
         <v>9</v>
@@ -1619,7 +1619,7 @@
         <v>24</v>
       </c>
       <c r="G8" s="5" t="s">
-        <v>139</v>
+        <v>127</v>
       </c>
       <c r="H8" s="5" t="s">
         <v>12</v>
@@ -1705,7 +1705,7 @@
         <v>33</v>
       </c>
       <c r="G10" s="13" t="s">
-        <v>140</v>
+        <v>128</v>
       </c>
       <c r="H10" s="13" t="s">
         <v>34</v>
@@ -1748,7 +1748,7 @@
         <v>37</v>
       </c>
       <c r="G11" s="6" t="s">
-        <v>140</v>
+        <v>128</v>
       </c>
       <c r="H11" s="6" t="s">
         <v>34</v>
@@ -1782,7 +1782,7 @@
         <v>30</v>
       </c>
       <c r="D12" s="53" t="s">
-        <v>137</v>
+        <v>125</v>
       </c>
       <c r="E12" s="14" t="s">
         <v>32</v>
@@ -1834,7 +1834,7 @@
         <v>45</v>
       </c>
       <c r="G13" s="7" t="s">
-        <v>141</v>
+        <v>129</v>
       </c>
       <c r="H13" s="7" t="s">
         <v>46</v>
@@ -1877,7 +1877,7 @@
         <v>49</v>
       </c>
       <c r="G14" s="7" t="s">
-        <v>142</v>
+        <v>130</v>
       </c>
       <c r="H14" s="7" t="s">
         <v>46</v>
@@ -1920,7 +1920,7 @@
         <v>52</v>
       </c>
       <c r="G15" s="7" t="s">
-        <v>142</v>
+        <v>130</v>
       </c>
       <c r="H15" s="7" t="s">
         <v>46</v>
@@ -1954,7 +1954,7 @@
         <v>42</v>
       </c>
       <c r="D16" s="62" t="s">
-        <v>135</v>
+        <v>123</v>
       </c>
       <c r="E16" s="7" t="s">
         <v>44</v>
@@ -1963,7 +1963,7 @@
         <v>54</v>
       </c>
       <c r="G16" s="7" t="s">
-        <v>143</v>
+        <v>131</v>
       </c>
       <c r="H16" s="7" t="s">
         <v>46</v>
@@ -1997,7 +1997,7 @@
         <v>42</v>
       </c>
       <c r="D17" s="62" t="s">
-        <v>136</v>
+        <v>124</v>
       </c>
       <c r="E17" s="7" t="s">
         <v>44</v>
@@ -2049,7 +2049,7 @@
         <v>61</v>
       </c>
       <c r="G18" s="15" t="s">
-        <v>144</v>
+        <v>132</v>
       </c>
       <c r="H18" s="15" t="s">
         <v>62</v>
@@ -2083,7 +2083,7 @@
         <v>58</v>
       </c>
       <c r="D19" s="60" t="s">
-        <v>133</v>
+        <v>121</v>
       </c>
       <c r="E19" s="8" t="s">
         <v>60</v>
@@ -2092,7 +2092,7 @@
         <v>64</v>
       </c>
       <c r="G19" s="8" t="s">
-        <v>145</v>
+        <v>133</v>
       </c>
       <c r="H19" s="8" t="s">
         <v>62</v>
@@ -2135,7 +2135,7 @@
         <v>67</v>
       </c>
       <c r="G20" s="8" t="s">
-        <v>146</v>
+        <v>134</v>
       </c>
       <c r="H20" s="8" t="s">
         <v>62</v>
@@ -2169,7 +2169,7 @@
         <v>58</v>
       </c>
       <c r="D21" s="61" t="s">
-        <v>134</v>
+        <v>122</v>
       </c>
       <c r="E21" s="16" t="s">
         <v>60</v>
@@ -2178,7 +2178,7 @@
         <v>69</v>
       </c>
       <c r="G21" s="16" t="s">
-        <v>144</v>
+        <v>132</v>
       </c>
       <c r="H21" s="16" t="s">
         <v>62</v>
@@ -2255,7 +2255,7 @@
         <v>71</v>
       </c>
       <c r="D23" s="59" t="s">
-        <v>132</v>
+        <v>120</v>
       </c>
       <c r="E23" s="9" t="s">
         <v>73</v>
@@ -2298,7 +2298,7 @@
         <v>71</v>
       </c>
       <c r="D24" s="59" t="s">
-        <v>131</v>
+        <v>119</v>
       </c>
       <c r="E24" s="9" t="s">
         <v>73</v>
@@ -2341,22 +2341,22 @@
         <v>83</v>
       </c>
       <c r="D25" s="17" t="s">
-        <v>84</v>
+        <v>142</v>
       </c>
       <c r="E25" s="17" t="s">
-        <v>85</v>
+        <v>148</v>
       </c>
       <c r="F25" s="17" t="s">
-        <v>86</v>
+        <v>149</v>
       </c>
       <c r="G25" s="17" t="s">
+        <v>139</v>
+      </c>
+      <c r="H25" s="17" t="s">
         <v>147</v>
       </c>
-      <c r="H25" s="17" t="s">
-        <v>87</v>
-      </c>
       <c r="I25" s="30" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="J25" s="1"/>
       <c r="K25" s="1"/>
@@ -2384,22 +2384,22 @@
         <v>83</v>
       </c>
       <c r="D26" s="58" t="s">
-        <v>130</v>
+        <v>143</v>
       </c>
       <c r="E26" s="10" t="s">
-        <v>85</v>
+        <v>148</v>
       </c>
       <c r="F26" s="10" t="s">
-        <v>89</v>
+        <v>150</v>
       </c>
       <c r="G26" s="10" t="s">
-        <v>148</v>
+        <v>140</v>
       </c>
       <c r="H26" s="10" t="s">
-        <v>87</v>
+        <v>147</v>
       </c>
       <c r="I26" s="31" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="J26" s="1"/>
       <c r="K26" s="1"/>
@@ -2427,22 +2427,22 @@
         <v>83</v>
       </c>
       <c r="D27" s="10" t="s">
-        <v>91</v>
+        <v>144</v>
       </c>
       <c r="E27" s="10" t="s">
-        <v>85</v>
+        <v>148</v>
       </c>
       <c r="F27" s="10" t="s">
-        <v>92</v>
+        <v>151</v>
       </c>
       <c r="G27" s="10" t="s">
-        <v>149</v>
+        <v>141</v>
       </c>
       <c r="H27" s="10" t="s">
-        <v>87</v>
+        <v>147</v>
       </c>
       <c r="I27" s="31" t="s">
-        <v>93</v>
+        <v>86</v>
       </c>
       <c r="J27" s="1"/>
       <c r="K27" s="1"/>
@@ -2470,22 +2470,22 @@
         <v>83</v>
       </c>
       <c r="D28" s="58" t="s">
-        <v>129</v>
+        <v>145</v>
       </c>
       <c r="E28" s="10" t="s">
-        <v>85</v>
+        <v>148</v>
       </c>
       <c r="F28" s="10" t="s">
-        <v>94</v>
+        <v>152</v>
       </c>
       <c r="G28" s="10" t="s">
         <v>28</v>
       </c>
       <c r="H28" s="10" t="s">
-        <v>87</v>
+        <v>147</v>
       </c>
       <c r="I28" s="31" t="s">
-        <v>95</v>
+        <v>87</v>
       </c>
       <c r="J28" s="1"/>
       <c r="K28" s="1"/>
@@ -2513,22 +2513,22 @@
         <v>83</v>
       </c>
       <c r="D29" s="18" t="s">
-        <v>96</v>
+        <v>146</v>
       </c>
       <c r="E29" s="18" t="s">
-        <v>85</v>
+        <v>148</v>
       </c>
       <c r="F29" s="18" t="s">
-        <v>97</v>
+        <v>153</v>
       </c>
       <c r="G29" s="18" t="s">
+        <v>139</v>
+      </c>
+      <c r="H29" s="18" t="s">
         <v>147</v>
       </c>
-      <c r="H29" s="18" t="s">
-        <v>87</v>
-      </c>
       <c r="I29" s="32" t="s">
-        <v>98</v>
+        <v>88</v>
       </c>
       <c r="J29" s="1"/>
       <c r="K29" s="1"/>
@@ -2553,25 +2553,25 @@
       <c r="A30" s="1"/>
       <c r="B30" s="1"/>
       <c r="C30" s="49" t="s">
-        <v>99</v>
+        <v>89</v>
       </c>
       <c r="D30" s="11" t="s">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="E30" s="11" t="s">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="F30" s="11" t="s">
-        <v>102</v>
+        <v>92</v>
       </c>
       <c r="G30" s="11" t="s">
-        <v>150</v>
+        <v>135</v>
       </c>
       <c r="H30" s="11" t="s">
-        <v>103</v>
+        <v>93</v>
       </c>
       <c r="I30" s="33" t="s">
-        <v>104</v>
+        <v>94</v>
       </c>
       <c r="J30" s="1"/>
       <c r="K30" s="1"/>
@@ -2596,25 +2596,25 @@
       <c r="A31" s="1"/>
       <c r="B31" s="1"/>
       <c r="C31" s="49" t="s">
-        <v>99</v>
+        <v>89</v>
       </c>
       <c r="D31" s="57" t="s">
-        <v>128</v>
+        <v>118</v>
       </c>
       <c r="E31" s="11" t="s">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="F31" s="11" t="s">
-        <v>105</v>
+        <v>95</v>
       </c>
       <c r="G31" s="11" t="s">
-        <v>151</v>
+        <v>136</v>
       </c>
       <c r="H31" s="11" t="s">
-        <v>103</v>
+        <v>93</v>
       </c>
       <c r="I31" s="33" t="s">
-        <v>106</v>
+        <v>96</v>
       </c>
       <c r="J31" s="1"/>
       <c r="K31" s="1"/>
@@ -2639,25 +2639,25 @@
       <c r="A32" s="1"/>
       <c r="B32" s="1"/>
       <c r="C32" s="49" t="s">
-        <v>99</v>
+        <v>89</v>
       </c>
       <c r="D32" s="11" t="s">
-        <v>107</v>
+        <v>97</v>
       </c>
       <c r="E32" s="11" t="s">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="F32" s="11" t="s">
-        <v>108</v>
+        <v>98</v>
       </c>
       <c r="G32" s="11" t="s">
-        <v>152</v>
+        <v>137</v>
       </c>
       <c r="H32" s="11" t="s">
-        <v>103</v>
+        <v>93</v>
       </c>
       <c r="I32" s="33" t="s">
-        <v>109</v>
+        <v>99</v>
       </c>
       <c r="J32" s="1"/>
       <c r="K32" s="1"/>
@@ -2682,25 +2682,25 @@
       <c r="A33" s="1"/>
       <c r="B33" s="1"/>
       <c r="C33" s="49" t="s">
-        <v>99</v>
+        <v>89</v>
       </c>
       <c r="D33" s="57" t="s">
-        <v>127</v>
+        <v>117</v>
       </c>
       <c r="E33" s="11" t="s">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="F33" s="11" t="s">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="G33" s="11" t="s">
-        <v>153</v>
+        <v>138</v>
       </c>
       <c r="H33" s="11" t="s">
-        <v>103</v>
+        <v>93</v>
       </c>
       <c r="I33" s="33" t="s">
-        <v>111</v>
+        <v>101</v>
       </c>
       <c r="J33" s="1"/>
       <c r="K33" s="1"/>
@@ -2725,25 +2725,25 @@
       <c r="A34" s="1"/>
       <c r="B34" s="1"/>
       <c r="C34" s="49" t="s">
-        <v>99</v>
+        <v>89</v>
       </c>
       <c r="D34" s="57" t="s">
-        <v>126</v>
+        <v>116</v>
       </c>
       <c r="E34" s="11" t="s">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="F34" s="11" t="s">
-        <v>112</v>
+        <v>102</v>
       </c>
       <c r="G34" s="11" t="s">
         <v>28</v>
       </c>
       <c r="H34" s="11" t="s">
-        <v>103</v>
+        <v>93</v>
       </c>
       <c r="I34" s="33" t="s">
-        <v>113</v>
+        <v>103</v>
       </c>
       <c r="J34" s="1"/>
       <c r="K34" s="1"/>
@@ -2768,25 +2768,25 @@
       <c r="A35" s="1"/>
       <c r="B35" s="1"/>
       <c r="C35" s="50" t="s">
-        <v>114</v>
+        <v>104</v>
       </c>
       <c r="D35" s="19" t="s">
-        <v>115</v>
+        <v>105</v>
       </c>
       <c r="E35" s="19" t="s">
-        <v>116</v>
+        <v>106</v>
       </c>
       <c r="F35" s="19" t="s">
-        <v>117</v>
+        <v>107</v>
       </c>
       <c r="G35" s="19" t="s">
         <v>28</v>
       </c>
       <c r="H35" s="19" t="s">
-        <v>118</v>
+        <v>108</v>
       </c>
       <c r="I35" s="34" t="s">
-        <v>119</v>
+        <v>109</v>
       </c>
       <c r="J35" s="1"/>
       <c r="K35" s="1"/>
@@ -2811,25 +2811,25 @@
       <c r="A36" s="1"/>
       <c r="B36" s="1"/>
       <c r="C36" s="51" t="s">
-        <v>114</v>
+        <v>104</v>
       </c>
       <c r="D36" s="56" t="s">
-        <v>125</v>
+        <v>115</v>
       </c>
       <c r="E36" s="12" t="s">
-        <v>116</v>
+        <v>106</v>
       </c>
       <c r="F36" s="12" t="s">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="G36" s="12" t="s">
         <v>28</v>
       </c>
       <c r="H36" s="12" t="s">
-        <v>118</v>
+        <v>108</v>
       </c>
       <c r="I36" s="35" t="s">
-        <v>121</v>
+        <v>111</v>
       </c>
       <c r="J36" s="1"/>
       <c r="K36" s="1"/>
@@ -2854,25 +2854,25 @@
       <c r="A37" s="1"/>
       <c r="B37" s="1"/>
       <c r="C37" s="52" t="s">
+        <v>104</v>
+      </c>
+      <c r="D37" s="55" t="s">
         <v>114</v>
       </c>
-      <c r="D37" s="55" t="s">
-        <v>124</v>
-      </c>
       <c r="E37" s="20" t="s">
-        <v>116</v>
+        <v>106</v>
       </c>
       <c r="F37" s="20" t="s">
-        <v>122</v>
+        <v>112</v>
       </c>
       <c r="G37" s="20" t="s">
         <v>28</v>
       </c>
       <c r="H37" s="20" t="s">
-        <v>118</v>
+        <v>108</v>
       </c>
       <c r="I37" s="36" t="s">
-        <v>123</v>
+        <v>113</v>
       </c>
       <c r="J37" s="1"/>
       <c r="K37" s="1"/>
